--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2023/NORTH_CAROLINA_2023.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2023/NORTH_CAROLINA_2023.xlsx
@@ -3876,7 +3876,7 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>General Simon Bolivar</t>
+          <t>Gral. Simon Bolivar</t>
         </is>
       </c>
       <c r="C196">
@@ -6252,7 +6252,7 @@
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
+          <t>Dolores Hidalgo</t>
         </is>
       </c>
       <c r="C328">
@@ -8790,7 +8790,7 @@
       </c>
       <c r="B469" t="inlineStr">
         <is>
-          <t>Huichapa</t>
+          <t>Huichapan</t>
         </is>
       </c>
       <c r="C469">
